--- a/Data/Home/Bathroom.TowelDryer001.xlsx
+++ b/Data/Home/Bathroom.TowelDryer001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:I319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709249912</v>
+        <v>1711841923</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709251953</v>
+        <v>1711844812</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -550,7 +557,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709278655</v>
+        <v>1711874779</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -569,14 +576,15 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -586,7 +594,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709280372</v>
+        <v>1711877009</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -605,7 +613,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -613,6 +621,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709281893</v>
+        <v>1711877928</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -646,9 +655,10 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -658,7 +668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709284480</v>
+        <v>1711893395</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -677,14 +687,15 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709284693</v>
+        <v>1711895620</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -718,9 +729,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709244175</v>
+        <v>1711899469</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709245752</v>
+        <v>1711927163</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -802,7 +816,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709267091</v>
+        <v>1711929528</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -821,14 +835,15 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709268387</v>
+        <v>1711962975</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -862,9 +877,10 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -874,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709269214</v>
+        <v>1711965295</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -893,14 +909,15 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709276942</v>
+        <v>1711967782</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -934,9 +951,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709283542</v>
+        <v>1711971796</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709329896</v>
+        <v>1711972096</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1006,9 +1025,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709331514</v>
+        <v>1711973548</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1054,7 +1075,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709350860</v>
+        <v>1711973980</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1073,7 +1094,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1081,6 +1102,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1090,7 +1112,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709352459</v>
+        <v>1711975812</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1109,14 +1131,15 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709361873</v>
+        <v>1711977214</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1162,7 +1186,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709362777</v>
+        <v>1711979873</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1181,14 +1205,15 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709364484</v>
+        <v>1712014701</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1222,9 +1247,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709368688</v>
+        <v>1712018700</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709416740</v>
+        <v>1712050651</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709418157</v>
+        <v>1712052273</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709448026</v>
+        <v>1712052982</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1366,9 +1395,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1378,7 +1408,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709449277</v>
+        <v>1712054117</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1397,7 +1427,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1405,6 +1435,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1414,7 +1445,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709451041</v>
+        <v>1712058939</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1433,14 +1464,15 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1450,7 +1482,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709454118</v>
+        <v>1712060377</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1469,7 +1501,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709454701</v>
+        <v>1712101141</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1522,7 +1556,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709455355</v>
+        <v>1712103314</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1541,7 +1575,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709456242</v>
+        <v>1712141392</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1582,9 +1617,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709462473</v>
+        <v>1712141630</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1618,9 +1654,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709502102</v>
+        <v>1712142210</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709503878</v>
+        <v>1712142297</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1690,9 +1728,10 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1702,7 +1741,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709530172</v>
+        <v>1712146275</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1721,14 +1760,15 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1738,7 +1778,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709533866</v>
+        <v>1712147275</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1757,14 +1797,15 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709535863</v>
+        <v>1712148546</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709535999</v>
+        <v>1712149565</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709542909</v>
+        <v>1712187407</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709588627</v>
+        <v>1712189708</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709590648</v>
+        <v>1712217540</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1942,9 +1987,10 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709615246</v>
+        <v>1712218650</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1978,9 +2024,10 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1990,7 +2037,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709618606</v>
+        <v>1712219338</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2009,14 +2056,15 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709620073</v>
+        <v>1712221270</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2101,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709621551</v>
+        <v>1712224223</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2138,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2157,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709622470</v>
+        <v>1712225329</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2175,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709623484</v>
+        <v>1712226730</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2212,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2170,7 +2222,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2179,7 +2231,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709627700</v>
+        <v>1712226945</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2189,7 +2241,7 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2197,6 +2249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2268,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709628539</v>
+        <v>1712273862</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2286,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2305,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709628804</v>
+        <v>1712277716</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2323,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2278,7 +2333,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2287,7 +2342,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709633894</v>
+        <v>1712306803</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2297,14 +2352,15 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2314,7 +2370,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2323,7 +2379,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709680020</v>
+        <v>1712308860</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2333,7 +2389,7 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2341,6 +2397,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2416,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709680961</v>
+        <v>1712309025</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2374,9 +2431,10 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2453,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709682552</v>
+        <v>1712317238</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2471,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2490,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709692728</v>
+        <v>1712323986</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2508,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2527,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709693288</v>
+        <v>1712363750</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2545,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2564,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709694189</v>
+        <v>1712365734</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2582,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2530,7 +2592,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2539,7 +2601,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709702029</v>
+        <v>1712367755</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2549,7 +2611,7 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2557,6 +2619,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2638,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709702379</v>
+        <v>1712382844</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2656,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2602,7 +2666,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2611,7 +2675,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709709504</v>
+        <v>1712383109</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2621,7 +2685,7 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2629,6 +2693,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2638,7 +2703,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2647,7 +2712,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709711719</v>
+        <v>1712392830</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2657,7 +2722,7 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2665,6 +2730,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2749,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709716373</v>
+        <v>1712394615</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2767,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2786,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709716904</v>
+        <v>1712400411</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2804,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2746,7 +2814,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2755,7 +2823,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709717125</v>
+        <v>1712400661</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2765,7 +2833,7 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2773,6 +2841,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2860,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709766835</v>
+        <v>1712402647</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2878,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2897,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709768722</v>
+        <v>1712408608</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +2915,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2934,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709769597</v>
+        <v>1712412397</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2878,9 +2949,10 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +2971,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709770223</v>
+        <v>1712451660</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +2989,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2926,7 +2999,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2935,7 +3008,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709770815</v>
+        <v>1712454576</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2945,14 +3018,15 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3045,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709777607</v>
+        <v>1712456477</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3063,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3082,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709786883</v>
+        <v>1712456980</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3022,9 +3097,10 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3119,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709788778</v>
+        <v>1712465711</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3137,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3156,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709796627</v>
+        <v>1712466770</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3174,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3193,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709797151</v>
+        <v>1712467360</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3211,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3142,7 +3221,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3151,7 +3230,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709799521</v>
+        <v>1712473381</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3161,7 +3240,7 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3169,6 +3248,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3267,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709801096</v>
+        <v>1712481627</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3285,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3304,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709804712</v>
+        <v>1712486010</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3322,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3341,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709848565</v>
+        <v>1712487887</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3277,6 +3359,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3286,7 +3369,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3295,7 +3378,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709851948</v>
+        <v>1712491817</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3305,7 +3388,7 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3313,6 +3396,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3322,7 +3406,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3331,7 +3415,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709873545</v>
+        <v>1712496397</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3341,14 +3425,15 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3452,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709873860</v>
+        <v>1712498897</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3385,6 +3470,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3489,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709874910</v>
+        <v>1712506184</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3418,9 +3504,10 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3526,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709879686</v>
+        <v>1712532794</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3457,6 +3544,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3466,7 +3554,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3475,7 +3563,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709883531</v>
+        <v>1712535128</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3485,7 +3573,7 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3493,6 +3581,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3600,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709935725</v>
+        <v>1712561962</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3618,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3637,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709937894</v>
+        <v>1712569823</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3565,6 +3655,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3674,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709965164</v>
+        <v>1712570728</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3598,9 +3689,10 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,7 +3711,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709967649</v>
+        <v>1712571991</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3637,6 +3729,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3646,7 +3739,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3655,7 +3748,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709967879</v>
+        <v>1712572932</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3665,7 +3758,7 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3673,6 +3766,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3691,7 +3785,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709969663</v>
+        <v>1712619188</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3706,9 +3800,10 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3718,7 +3813,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3727,7 +3822,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709972932</v>
+        <v>1712623607</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3737,14 +3832,15 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3754,7 +3850,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3763,7 +3859,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709973467</v>
+        <v>1712645655</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3773,14 +3869,15 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +3896,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709974635</v>
+        <v>1712647794</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3814,9 +3911,10 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3826,7 +3924,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3835,7 +3933,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709974933</v>
+        <v>1712654821</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3845,14 +3943,15 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +3970,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710021865</v>
+        <v>1712656666</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3889,6 +3988,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4007,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710023571</v>
+        <v>1712657272</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3922,9 +4022,10 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4044,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710034813</v>
+        <v>1712657566</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3961,6 +4062,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4081,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710050796</v>
+        <v>1712659367</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3994,9 +4096,10 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4118,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710051988</v>
+        <v>1712660535</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4033,6 +4136,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4051,7 +4155,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710052765</v>
+        <v>1712661360</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4069,6 +4173,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4192,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710053991</v>
+        <v>1712668881</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4105,6 +4210,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4114,7 +4220,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4123,7 +4229,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710056280</v>
+        <v>1712705644</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4133,14 +4239,15 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4266,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710058108</v>
+        <v>1712707778</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4174,9 +4281,10 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4186,7 +4294,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4195,7 +4303,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710058352</v>
+        <v>1712737227</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4205,14 +4313,15 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4340,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710107515</v>
+        <v>1712739075</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4246,9 +4355,10 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4258,7 +4368,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4267,7 +4377,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710108968</v>
+        <v>1712744888</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4277,7 +4387,7 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4285,6 +4395,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4414,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710129204</v>
+        <v>1712746211</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4432,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4451,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710135542</v>
+        <v>1712754779</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4469,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4488,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710135716</v>
+        <v>1712755745</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4506,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4525,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710137052</v>
+        <v>1712756637</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4543,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4447,7 +4562,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710150891</v>
+        <v>1712763850</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4465,6 +4580,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4483,7 +4599,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710195618</v>
+        <v>1712791088</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4501,6 +4617,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4519,7 +4636,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710198180</v>
+        <v>1712793532</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4537,6 +4654,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4555,7 +4673,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710221946</v>
+        <v>1712820957</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4573,6 +4691,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4591,7 +4710,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710223938</v>
+        <v>1712822925</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4609,6 +4728,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4618,7 +4738,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4627,7 +4747,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710225948</v>
+        <v>1712824222</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4637,7 +4757,7 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4645,6 +4765,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4654,7 +4775,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4663,7 +4784,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710226065</v>
+        <v>1712828609</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4673,7 +4794,7 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4681,6 +4802,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4690,7 +4812,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4699,7 +4821,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710226328</v>
+        <v>1712830504</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4709,14 +4831,15 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4735,7 +4858,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710227740</v>
+        <v>1712830956</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4753,6 +4876,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4771,7 +4895,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710228343</v>
+        <v>1712831332</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4789,6 +4913,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4807,7 +4932,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710234563</v>
+        <v>1712832524</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4825,6 +4950,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4843,7 +4969,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710236249</v>
+        <v>1712877650</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4861,6 +4987,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4879,7 +5006,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710236961</v>
+        <v>1712879655</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4894,9 +5021,10 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4906,7 +5034,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4915,7 +5043,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710243388</v>
+        <v>1712912988</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4925,14 +5053,15 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4942,7 +5071,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4951,7 +5080,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710289989</v>
+        <v>1712914963</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4961,7 +5090,7 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -4969,6 +5098,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4987,7 +5117,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710290380</v>
+        <v>1712915605</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5005,6 +5135,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5014,7 +5145,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5023,7 +5154,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710291576</v>
+        <v>1712919134</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5033,14 +5164,15 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5059,7 +5191,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710292044</v>
+        <v>1712924002</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5074,9 +5206,10 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5095,7 +5228,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710292332</v>
+        <v>1712972191</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5113,6 +5246,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5122,7 +5256,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5131,7 +5265,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710293550</v>
+        <v>1712973226</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5141,14 +5275,15 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5158,7 +5293,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5167,7 +5302,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710300676</v>
+        <v>1712974565</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5177,7 +5312,7 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5185,6 +5320,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5194,7 +5330,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5203,7 +5339,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710301629</v>
+        <v>1712974964</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5213,14 +5349,15 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5239,7 +5376,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710307255</v>
+        <v>1712975486</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5254,9 +5391,10 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5275,7 +5413,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710311111</v>
+        <v>1712975649</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -5293,6 +5431,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5311,7 +5450,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710313734</v>
+        <v>1712977156</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5326,9 +5465,10 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5338,7 +5478,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5347,7 +5487,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710317589</v>
+        <v>1712991019</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5357,7 +5497,7 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5365,6 +5505,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5383,7 +5524,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710318153</v>
+        <v>1712997091</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5401,6 +5542,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5419,7 +5561,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710318471</v>
+        <v>1712999664</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -5437,6 +5579,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5455,7 +5598,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710319561</v>
+        <v>1713005844</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5470,9 +5613,10 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5482,7 +5626,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5491,7 +5635,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710320958</v>
+        <v>1713006109</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5501,7 +5645,7 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5509,6 +5653,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5518,7 +5663,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5527,7 +5672,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710322101</v>
+        <v>1713011193</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5537,7 +5682,7 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5545,6 +5690,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5563,7 +5709,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710322419</v>
+        <v>1713012844</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5578,9 +5724,10 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5599,7 +5746,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710322813</v>
+        <v>1713014655</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5617,6 +5764,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5635,7 +5783,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710324750</v>
+        <v>1713016070</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5653,6 +5801,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5671,7 +5820,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710326611</v>
+        <v>1713019859</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5689,6 +5838,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5698,7 +5848,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5707,7 +5857,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710330057</v>
+        <v>1713056862</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5717,7 +5867,7 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -5725,6 +5875,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5734,7 +5885,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5743,7 +5894,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710371563</v>
+        <v>1713058343</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5753,7 +5904,7 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -5761,6 +5912,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5779,7 +5931,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710373122</v>
+        <v>1713059229</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5797,6 +5949,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5815,7 +5968,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710374655</v>
+        <v>1713059651</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5830,9 +5983,10 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5842,7 +5996,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5851,7 +6005,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710386027</v>
+        <v>1713089276</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5861,7 +6015,7 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -5869,6 +6023,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5887,7 +6042,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710387015</v>
+        <v>1713089400</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5905,6 +6060,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5914,7 +6070,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5923,7 +6079,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710392108</v>
+        <v>1713093565</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5933,7 +6089,7 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -5941,6 +6097,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5959,7 +6116,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710395015</v>
+        <v>1713097931</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5977,6 +6134,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5995,7 +6153,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710400559</v>
+        <v>1713100421</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -6013,6 +6171,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6031,7 +6190,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710401610</v>
+        <v>1713102012</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -6049,6 +6208,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6067,7 +6227,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710401842</v>
+        <v>1713103112</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -6085,6 +6245,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6103,7 +6264,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710403125</v>
+        <v>1713108412</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -6121,6 +6282,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6139,7 +6301,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710406658</v>
+        <v>1713108541</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -6157,6 +6319,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6175,7 +6338,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710408089</v>
+        <v>1713137628</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -6193,6 +6356,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6211,7 +6375,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710409411</v>
+        <v>1713139643</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6229,6 +6393,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6238,7 +6403,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6247,7 +6412,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710455385</v>
+        <v>1713168828</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -6257,7 +6422,7 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6265,6 +6430,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6283,7 +6449,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710457343</v>
+        <v>1713176309</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -6301,6 +6467,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6319,7 +6486,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710486848</v>
+        <v>1713177888</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -6334,9 +6501,10 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6355,7 +6523,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710487306</v>
+        <v>1713179867</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6370,9 +6538,10 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6391,7 +6560,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710488263</v>
+        <v>1713186030</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -6409,6 +6578,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6427,7 +6597,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710488625</v>
+        <v>1713223697</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -6442,9 +6612,10 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6454,7 +6625,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6463,7 +6634,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710490354</v>
+        <v>1713226112</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -6473,14 +6644,15 @@
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6499,7 +6671,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710491837</v>
+        <v>1713259148</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6514,9 +6686,10 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6535,7 +6708,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710494480</v>
+        <v>1713264403</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6553,6 +6726,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6571,7 +6745,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710494879</v>
+        <v>1713267447</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -6589,6 +6763,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6598,7 +6773,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6607,7 +6782,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710540477</v>
+        <v>1713269197</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6617,14 +6792,15 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6643,7 +6819,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710541697</v>
+        <v>1713271182</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -6658,9 +6834,10 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6679,7 +6856,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710563580</v>
+        <v>1713275526</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6697,6 +6874,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6715,7 +6893,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710564919</v>
+        <v>1713276206</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6730,9 +6908,10 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6742,7 +6921,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6751,7 +6930,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710568106</v>
+        <v>1713277931</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6761,14 +6940,15 @@
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6787,7 +6967,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710569274</v>
+        <v>1713279027</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6805,6 +6985,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6814,7 +6995,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6823,7 +7004,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710571055</v>
+        <v>1713310477</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6833,14 +7014,15 @@
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6850,7 +7032,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6859,7 +7041,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710572067</v>
+        <v>1713314028</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6869,7 +7051,7 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -6877,6 +7059,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6895,7 +7078,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710572076</v>
+        <v>1713346896</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6910,9 +7093,10 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6931,7 +7115,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710572675</v>
+        <v>1713347862</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6946,9 +7130,10 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6958,7 +7143,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6967,7 +7152,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710576795</v>
+        <v>1713348444</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6977,7 +7162,7 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -6985,6 +7170,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6994,7 +7180,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7003,7 +7189,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710626533</v>
+        <v>1713349050</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -7013,7 +7199,7 @@
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -7021,6 +7207,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7030,7 +7217,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7039,7 +7226,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710628175</v>
+        <v>1713350807</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -7049,7 +7236,7 @@
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -7057,6 +7244,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7075,7 +7263,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710655028</v>
+        <v>1713351312</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -7093,6 +7281,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7111,7 +7300,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710657746</v>
+        <v>1713354912</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -7129,6 +7318,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7138,7 +7328,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7147,7 +7337,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710660463</v>
+        <v>1713355707</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -7157,14 +7347,15 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7183,7 +7374,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710661036</v>
+        <v>1713396254</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7201,6 +7392,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7219,7 +7411,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710661954</v>
+        <v>1713398541</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -7234,9 +7426,10 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7255,7 +7448,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710713057</v>
+        <v>1713439537</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -7273,6 +7466,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7282,7 +7476,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7291,7 +7485,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1710715164</v>
+        <v>1713440534</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -7301,14 +7495,15 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7318,7 +7513,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7327,7 +7522,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1710739099</v>
+        <v>1713440892</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7337,14 +7532,15 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7363,7 +7559,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1710740188</v>
+        <v>1713442752</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -7378,9 +7574,10 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7390,7 +7587,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7399,7 +7596,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1710740606</v>
+        <v>1713446877</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -7409,7 +7606,7 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -7417,6 +7614,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7426,7 +7624,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7435,7 +7633,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1710748192</v>
+        <v>1713447266</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -7445,7 +7643,7 @@
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -7453,6 +7651,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7471,7 +7670,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1710749772</v>
+        <v>1713449280</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -7486,9 +7685,10 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7507,7 +7707,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1710750346</v>
+        <v>1713482825</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7522,9 +7722,10 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7534,7 +7735,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7543,7 +7744,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1710756234</v>
+        <v>1713487209</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7553,7 +7754,7 @@
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -7561,6 +7762,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7579,7 +7781,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1710799073</v>
+        <v>1713521473</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7597,6 +7799,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7606,7 +7809,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7615,7 +7818,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1710800794</v>
+        <v>1713521653</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -7625,7 +7828,7 @@
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -7633,6 +7836,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7642,7 +7846,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7651,7 +7855,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1710830862</v>
+        <v>1713527938</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -7661,14 +7865,15 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7678,7 +7883,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7687,7 +7892,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1710831221</v>
+        <v>1713530233</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -7697,7 +7902,7 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -7705,6 +7910,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7714,7 +7920,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7723,7 +7929,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1710833016</v>
+        <v>1713573626</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -7733,14 +7939,15 @@
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7750,7 +7957,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7759,7 +7966,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1710835382</v>
+        <v>1713575359</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7769,14 +7976,15 @@
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7795,7 +8003,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1710835654</v>
+        <v>1713577467</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -7813,6 +8021,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7822,7 +8031,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7831,7 +8040,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1710837207</v>
+        <v>1713591690</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7841,14 +8050,15 @@
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7858,7 +8068,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7867,7 +8077,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1710839609</v>
+        <v>1713593443</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7877,14 +8087,15 @@
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7903,7 +8114,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1710841475</v>
+        <v>1713602408</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7918,9 +8129,10 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7930,7 +8142,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7939,7 +8151,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1710889476</v>
+        <v>1713604628</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7949,7 +8161,7 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -7957,6 +8169,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7966,7 +8179,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7975,7 +8188,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1710890032</v>
+        <v>1713608009</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7985,7 +8198,7 @@
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -7993,6 +8206,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8011,7 +8225,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1710890837</v>
+        <v>1713609216</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -8029,6 +8243,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8047,7 +8262,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1710891589</v>
+        <v>1713610880</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -8065,6 +8280,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8083,7 +8299,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1710900083</v>
+        <v>1713612177</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -8101,6 +8317,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8119,7 +8336,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1710901847</v>
+        <v>1713614026</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -8137,6 +8354,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8155,7 +8373,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1710904185</v>
+        <v>1713615521</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -8173,6 +8391,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8191,7 +8410,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1710910355</v>
+        <v>1713615647</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -8209,6 +8428,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8227,7 +8447,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1710912790</v>
+        <v>1713620204</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -8245,6 +8465,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8263,7 +8484,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1710916385</v>
+        <v>1713624175</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -8281,6 +8502,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8299,7 +8521,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1710917690</v>
+        <v>1713626148</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -8317,6 +8539,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8326,7 +8549,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8335,7 +8558,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1710919387</v>
+        <v>1713659525</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -8345,7 +8568,7 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -8353,6 +8576,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8362,7 +8586,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8371,7 +8595,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1710920441</v>
+        <v>1713662202</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -8381,7 +8605,7 @@
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -8389,6 +8613,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8407,7 +8632,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1710921535</v>
+        <v>1713663621</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -8425,6 +8650,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8434,7 +8660,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8443,7 +8669,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1710922847</v>
+        <v>1713663721</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -8453,7 +8679,7 @@
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -8461,6 +8687,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8479,7 +8706,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1710924828</v>
+        <v>1713664723</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8494,9 +8721,10 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8506,7 +8734,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8515,7 +8743,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1710928837</v>
+        <v>1713665753</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8525,7 +8753,7 @@
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -8533,6 +8761,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8542,7 +8771,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8551,7 +8780,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1710975435</v>
+        <v>1713667248</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8561,7 +8790,7 @@
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -8569,6 +8798,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8578,7 +8808,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8587,7 +8817,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1710977148</v>
+        <v>1713675614</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -8597,7 +8827,7 @@
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -8605,6 +8835,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8623,7 +8854,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1710978489</v>
+        <v>1713677531</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -8641,6 +8872,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8650,7 +8882,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8659,7 +8891,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1710978775</v>
+        <v>1713682565</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -8669,14 +8901,15 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8686,7 +8919,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8695,7 +8928,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1710980044</v>
+        <v>1713686839</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -8705,7 +8938,7 @@
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -8713,6 +8946,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8731,7 +8965,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1710980592</v>
+        <v>1713688361</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -8746,9 +8980,10 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8758,7 +8993,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8767,7 +9002,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1710988393</v>
+        <v>1713689300</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -8777,14 +9012,15 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8803,7 +9039,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1710989670</v>
+        <v>1713690187</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -8821,6 +9057,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8839,7 +9076,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1710992412</v>
+        <v>1713692346</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -8857,6 +9094,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8875,7 +9113,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1710999929</v>
+        <v>1713695447</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -8893,6 +9131,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8902,7 +9141,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8911,7 +9150,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1711000546</v>
+        <v>1713697520</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -8921,7 +9160,7 @@
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -8929,6 +9168,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8938,7 +9178,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8947,7 +9187,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1711004781</v>
+        <v>1713700905</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8957,7 +9197,7 @@
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -8965,6 +9205,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8983,7 +9224,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1711006985</v>
+        <v>1713702334</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -9001,6 +9242,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9019,7 +9261,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1711008988</v>
+        <v>1713703260</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -9037,6 +9279,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9055,7 +9298,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1711011412</v>
+        <v>1713707082</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -9073,6 +9316,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9091,7 +9335,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1711014097</v>
+        <v>1713708534</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -9109,6 +9353,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9127,7 +9372,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1711014306</v>
+        <v>1713740935</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -9145,6 +9390,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9163,7 +9409,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1711058892</v>
+        <v>1713743507</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -9181,6 +9427,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9199,7 +9446,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1711061040</v>
+        <v>1713772807</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -9217,6 +9464,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9235,7 +9483,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1711085677</v>
+        <v>1713773561</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -9250,9 +9498,10 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9271,7 +9520,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1711087076</v>
+        <v>1713775510</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -9286,9 +9535,10 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9298,7 +9548,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9307,7 +9557,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1711088016</v>
+        <v>1713778732</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -9317,7 +9567,7 @@
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -9325,6 +9575,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9343,7 +9594,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1711091392</v>
+        <v>1713779430</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -9361,6 +9612,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9370,7 +9622,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9379,7 +9631,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1711092921</v>
+        <v>1713780610</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -9389,7 +9641,7 @@
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -9397,6 +9649,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9415,7 +9668,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1711098741</v>
+        <v>1713780865</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -9430,9 +9683,10 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9442,7 +9696,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9451,7 +9705,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1711145376</v>
+        <v>1713792863</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -9461,7 +9715,7 @@
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -9469,6 +9723,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9487,7 +9742,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1711147262</v>
+        <v>1713828386</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -9505,6 +9760,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9523,7 +9779,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1711170229</v>
+        <v>1713832347</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -9541,6 +9797,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9550,7 +9807,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9559,7 +9816,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1711174123</v>
+        <v>1713865657</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -9569,7 +9826,7 @@
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -9577,6 +9834,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9595,7 +9853,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1711175704</v>
+        <v>1713866848</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -9613,6 +9871,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9631,7 +9890,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1711178178</v>
+        <v>1713866904</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -9649,6 +9908,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9667,7 +9927,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1711179887</v>
+        <v>1713868108</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -9685,6 +9945,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9694,7 +9955,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9703,7 +9964,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1711182277</v>
+        <v>1713869077</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -9713,14 +9974,15 @@
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9739,7 +10001,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1711184010</v>
+        <v>1713875014</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -9757,6 +10019,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9775,7 +10038,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1711233114</v>
+        <v>1713875458</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -9793,6 +10056,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9802,7 +10066,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9811,7 +10075,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1711236364</v>
+        <v>1713915037</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -9821,7 +10085,7 @@
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -9829,6 +10093,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9847,7 +10112,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1711265228</v>
+        <v>1713917060</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -9862,9 +10127,10 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9883,7 +10149,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1711268586</v>
+        <v>1713944516</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -9901,6 +10167,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9910,7 +10177,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9919,7 +10186,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1711274449</v>
+        <v>1713952489</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -9929,14 +10196,15 @@
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9955,7 +10223,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1711275192</v>
+        <v>1713952923</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -9973,6 +10241,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9991,7 +10260,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1711319416</v>
+        <v>1713954654</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -10006,9 +10275,10 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -10018,7 +10288,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10027,7 +10297,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1711322663</v>
+        <v>1713962810</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -10037,7 +10307,7 @@
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -10045,6 +10315,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10063,7 +10334,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1711343995</v>
+        <v>1714001309</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -10081,6 +10352,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -10099,7 +10371,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1711350505</v>
+        <v>1714005852</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -10117,6 +10389,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10135,7 +10408,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1711352462</v>
+        <v>1714031639</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -10153,6 +10426,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10171,7 +10445,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1711354216</v>
+        <v>1714033517</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -10189,6 +10463,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -10198,7 +10473,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -10207,7 +10482,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1711355173</v>
+        <v>1714035573</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -10217,7 +10492,7 @@
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -10225,6 +10500,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10234,7 +10510,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -10243,7 +10519,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1711356551</v>
+        <v>1714038750</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -10253,7 +10529,7 @@
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -10261,6 +10537,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10279,7 +10556,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1711358118</v>
+        <v>1714043040</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -10297,6 +10574,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10315,7 +10593,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1711358860</v>
+        <v>1714053272</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -10330,9 +10608,10 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10342,7 +10621,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10351,7 +10630,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1711358895</v>
+        <v>1714087483</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -10361,7 +10640,7 @@
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -10369,6 +10648,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10387,7 +10667,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1711360090</v>
+        <v>1714090022</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -10405,6 +10685,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10414,7 +10695,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10423,7 +10704,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1711360507</v>
+        <v>1714127930</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -10433,7 +10714,7 @@
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -10441,6 +10722,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10459,7 +10741,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1711410126</v>
+        <v>1714129830</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -10477,6 +10759,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10486,7 +10769,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10495,7 +10778,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1711412595</v>
+        <v>1714131761</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -10505,14 +10788,15 @@
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10522,7 +10806,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -10531,7 +10815,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1711451478</v>
+        <v>1714134042</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -10541,7 +10825,7 @@
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -10549,6 +10833,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10567,7 +10852,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1711452393</v>
+        <v>1714138237</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -10585,6 +10870,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10603,7 +10889,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1711453377</v>
+        <v>1714177796</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -10618,9 +10904,10 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10639,7 +10926,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1711453602</v>
+        <v>1714179168</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -10654,9 +10941,10 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10666,7 +10954,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10675,7 +10963,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1711454887</v>
+        <v>1714181976</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -10685,7 +10973,7 @@
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -10693,6 +10981,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10711,7 +11000,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1711455671</v>
+        <v>1714183473</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -10726,9 +11015,10 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10747,7 +11037,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1711460666</v>
+        <v>1714197696</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -10765,6 +11055,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10774,7 +11065,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -10783,7 +11074,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1711503327</v>
+        <v>1714208330</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -10793,7 +11084,7 @@
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -10801,6 +11092,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10819,7 +11111,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1711504719</v>
+        <v>1714210252</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -10837,6 +11129,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10846,7 +11139,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -10855,7 +11148,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1711504965</v>
+        <v>1714212742</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -10865,7 +11158,7 @@
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -10873,6 +11166,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10891,7 +11185,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1711506167</v>
+        <v>1714214743</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -10906,9 +11200,10 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10918,7 +11213,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10927,7 +11222,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1711519996</v>
+        <v>1714215134</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -10937,14 +11232,15 @@
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10954,7 +11250,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -10963,7 +11259,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1711520636</v>
+        <v>1714217897</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -10973,7 +11269,7 @@
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -10981,6 +11277,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10999,7 +11296,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1711529651</v>
+        <v>1714221406</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -11017,6 +11314,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11026,7 +11324,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -11035,7 +11333,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1711531012</v>
+        <v>1714224589</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -11045,14 +11343,15 @@
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11071,7 +11370,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1711539889</v>
+        <v>1714225447</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -11089,6 +11388,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11107,7 +11407,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1711544270</v>
+        <v>1714226654</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -11125,6 +11425,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -11134,7 +11435,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11143,7 +11444,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1711546144</v>
+        <v>1714226809</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -11153,14 +11454,15 @@
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11179,7 +11481,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1711548793</v>
+        <v>1714231665</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -11197,6 +11499,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11215,7 +11518,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1711551065</v>
+        <v>1714232555</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -11233,6 +11536,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11242,7 +11546,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -11251,7 +11555,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1711556069</v>
+        <v>1714268356</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -11261,14 +11565,15 @@
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11278,7 +11583,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11287,7 +11592,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1711589810</v>
+        <v>1714269557</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -11297,7 +11602,7 @@
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: on</t>
+          <t>Bathroom.TowelDryer001.state: off</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -11305,6 +11610,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11323,7 +11629,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1711591134</v>
+        <v>1714270433</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -11338,9 +11644,10 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11359,7 +11666,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1711591320</v>
+        <v>1714271042</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -11377,6 +11684,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11395,7 +11703,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1711592763</v>
+        <v>1714271761</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -11413,6 +11721,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11431,7 +11740,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1711605924</v>
+        <v>1714271875</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -11449,6 +11758,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11467,7 +11777,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1711607865</v>
+        <v>1714273721</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -11485,6 +11795,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11503,7 +11814,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1711608835</v>
+        <v>1714283451</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -11521,6 +11832,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11539,7 +11851,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>1711609784</v>
+        <v>1714290732</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -11557,6 +11869,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11575,7 +11888,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1711621467</v>
+        <v>1714295801</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -11593,6 +11906,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11611,7 +11925,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1711621846</v>
+        <v>1714297129</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -11629,6 +11943,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11647,7 +11962,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1711623561</v>
+        <v>1714298460</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -11665,6 +11980,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11683,7 +11999,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1711624632</v>
+        <v>1714302983</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -11698,9 +12014,10 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11719,7 +12036,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1711625479</v>
+        <v>1714303475</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -11737,6 +12054,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11746,7 +12064,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>TowerDryer_Operation</t>
+          <t>TowelDryer_Operation</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -11755,7 +12073,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1711630585</v>
+        <v>1714306548</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -11765,7 +12083,7 @@
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Bathroom.TowelDryer001.state: off</t>
+          <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -11773,6 +12091,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11791,7 +12110,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1711630638</v>
+        <v>1714307740</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -11809,6 +12128,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11827,7 +12147,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1711634995</v>
+        <v>1714313050</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -11845,6 +12165,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11854,7 +12175,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>TowelDryer_Operation</t>
+          <t>TowerDryer_Operation</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -11863,7 +12184,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1711641075</v>
+        <v>1714313599</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -11873,14 +12194,52 @@
       <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
+          <t>Bathroom.TowelDryer001.state: off</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>TowelDryer_Operation</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Bathroom</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>1714313769</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
           <t>Bathroom.TowelDryer001.state: on</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
